--- a/ExcelFiles/ModelCalibration5Sectorsand1Regions_replication.xlsx
+++ b/ExcelFiles/ModelCalibration5Sectorsand1Regions_replication.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FF4933-496C-4E1A-86DC-FBEBE8CC1FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A042970-A39E-45D7-B9CB-8F3ED4C9E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="5415" windowWidth="38700" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="5" r:id="rId1"/>
